--- a/data/trans_orig/IMC_inf_MED_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IMC_inf_MED_R2-Estudios-trans_orig.xlsx
@@ -545,7 +545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen sobrepeso u obesidad, recogido por medición en 2012 (tasa de respuesta: 70,03%)</t>
+          <t>Menores según si tienen sobrepeso u obesidad, recogido por medición en 2012 (tasa de respuesta: 83,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -729,67 +729,67 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>28777</v>
+        <v>35288</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>22718</v>
+        <v>28329</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>35138</v>
+        <v>42573</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.5057636434845424</v>
+        <v>0.4657047840377311</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.3992703373934586</v>
+        <v>0.3738704411589819</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.6175504828726796</v>
+        <v>0.5618481108522054</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>33671</v>
+        <v>39252</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>27248</v>
+        <v>32104</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>40298</v>
+        <v>47221</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.5108885031659872</v>
+        <v>0.4871716962160342</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.4134386743246361</v>
+        <v>0.3984615763744734</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.6114507222405522</v>
+        <v>0.5860758036078983</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>62448</v>
+        <v>74539</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>53750</v>
+        <v>65455</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>71956</v>
+        <v>85698</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.5085140087609992</v>
+        <v>0.4767676386070236</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.4376841180034391</v>
+        <v>0.4186628126681232</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.5859388457435649</v>
+        <v>0.548137984756752</v>
       </c>
     </row>
     <row r="5">
@@ -800,67 +800,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>28122</v>
+        <v>40485</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>21761</v>
+        <v>33200</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>34181</v>
+        <v>47444</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.4942363565154576</v>
+        <v>0.5342952159622689</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.3824495171273204</v>
+        <v>0.4381518891477946</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.6007296626065414</v>
+        <v>0.626129558841018</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>32235</v>
+        <v>41319</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>25608</v>
+        <v>33350</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>38658</v>
+        <v>48467</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.4891114968340127</v>
+        <v>0.5128283037839658</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.3885492777594479</v>
+        <v>0.4139241963921017</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.5865613256753635</v>
+        <v>0.6015384236255266</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>60357</v>
+        <v>81804</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>50849</v>
+        <v>70645</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>69055</v>
+        <v>90888</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.4914859912390008</v>
+        <v>0.5232323613929764</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.414061154256435</v>
+        <v>0.451862015243248</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.5623158819965608</v>
+        <v>0.5813371873318768</v>
       </c>
     </row>
     <row r="6">
@@ -871,16 +871,16 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>56899</v>
+        <v>75773</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>56899</v>
+        <v>75773</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>56899</v>
+        <v>75773</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -892,16 +892,16 @@
         <v>1</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>65906</v>
+        <v>80571</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>65906</v>
+        <v>80571</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>65906</v>
+        <v>80571</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>1</v>
@@ -913,16 +913,16 @@
         <v>1</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>177</v>
+        <v>224</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>122805</v>
+        <v>156343</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>122805</v>
+        <v>156343</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>122805</v>
+        <v>156343</v>
       </c>
       <c r="U6" s="6" t="n">
         <v>1</v>
@@ -946,67 +946,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>273</v>
+        <v>312</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>189136</v>
+        <v>217419</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>172783</v>
+        <v>200828</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>203462</v>
+        <v>232902</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.5457758279679681</v>
+        <v>0.5288261011105012</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.4985858357537655</v>
+        <v>0.4884726317490961</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.5871143020206953</v>
+        <v>0.566484741474269</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>203</v>
+        <v>241</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>141822</v>
+        <v>168837</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>127965</v>
+        <v>153867</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>156919</v>
+        <v>184431</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.4477258520522747</v>
+        <v>0.4481518797374033</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.4039784387775912</v>
+        <v>0.4084147113164016</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.4953870135130423</v>
+        <v>0.4895421731203441</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>476</v>
+        <v>553</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>330958</v>
+        <v>386256</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>310542</v>
+        <v>363760</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>352639</v>
+        <v>411955</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.4989522486006108</v>
+        <v>0.4902498350798606</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.4681725396638418</v>
+        <v>0.4616966675203141</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.5316385238231466</v>
+        <v>0.5228675090506922</v>
       </c>
     </row>
     <row r="8">
@@ -1017,67 +1017,67 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>227</v>
+        <v>280</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>157410</v>
+        <v>193716</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>143084</v>
+        <v>178233</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>173763</v>
+        <v>210307</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.4542241720320319</v>
+        <v>0.4711738988894988</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.4128856979793047</v>
+        <v>0.433515258525731</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.5014141642462345</v>
+        <v>0.5115273682509038</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>254</v>
+        <v>301</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>174939</v>
+        <v>207904</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>159842</v>
+        <v>192310</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>188796</v>
+        <v>222874</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.5522741479477253</v>
+        <v>0.5518481202625967</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.5046129864869576</v>
+        <v>0.5104578268796558</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.5960215612224089</v>
+        <v>0.5915852886835985</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>481</v>
+        <v>581</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>332348</v>
+        <v>401620</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>310667</v>
+        <v>375921</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>352764</v>
+        <v>424116</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.5010477513993893</v>
+        <v>0.5097501649201394</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.4683614761768533</v>
+        <v>0.4771324909493078</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.5318274603361581</v>
+        <v>0.538303332479686</v>
       </c>
     </row>
     <row r="9">
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>500</v>
+        <v>592</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>346546</v>
+        <v>411135</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>346546</v>
+        <v>411135</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>346546</v>
+        <v>411135</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -1109,16 +1109,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>457</v>
+        <v>542</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>316761</v>
+        <v>376741</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>316761</v>
+        <v>376741</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>316761</v>
+        <v>376741</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -1130,16 +1130,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>957</v>
+        <v>1134</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>663306</v>
+        <v>787876</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>663306</v>
+        <v>787876</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>663306</v>
+        <v>787876</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -1163,67 +1163,67 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>63003</v>
+        <v>72373</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>53247</v>
+        <v>62028</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>72559</v>
+        <v>82086</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.5287758699899939</v>
+        <v>0.5232379028152686</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.4468941344762113</v>
+        <v>0.4484472320135177</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.6089818007262321</v>
+        <v>0.59345741107797</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>50021</v>
+        <v>59062</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>40484</v>
+        <v>48503</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>58550</v>
+        <v>68248</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.4238992612917087</v>
+        <v>0.425288711245244</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.3430737642995509</v>
+        <v>0.3492546652281304</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.4961753097062224</v>
+        <v>0.4914338170092301</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>113024</v>
+        <v>131436</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>100912</v>
+        <v>117684</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>126367</v>
+        <v>145298</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.4765906773035776</v>
+        <v>0.474164682737844</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.4255142362790962</v>
+        <v>0.4245555509442357</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.5328506220746122</v>
+        <v>0.5241744617539472</v>
       </c>
     </row>
     <row r="11">
@@ -1234,67 +1234,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>56145</v>
+        <v>65945</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>46589</v>
+        <v>56232</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>65901</v>
+        <v>76290</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.471224130010006</v>
+        <v>0.4767620971847313</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.391018199273768</v>
+        <v>0.40654258892203</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.5531058655237887</v>
+        <v>0.5515527679864823</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>67982</v>
+        <v>79814</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>59453</v>
+        <v>70628</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>77519</v>
+        <v>90373</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.5761007387082914</v>
+        <v>0.574711288754756</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.5038246902937775</v>
+        <v>0.5085661829907699</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.6569262357004491</v>
+        <v>0.6507453347718694</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>124128</v>
+        <v>145758</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>110785</v>
+        <v>131896</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>136240</v>
+        <v>159510</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.5234093226964225</v>
+        <v>0.525835317262156</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.4671493779253877</v>
+        <v>0.4758255382460527</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.5744857637209038</v>
+        <v>0.5754444490557643</v>
       </c>
     </row>
     <row r="12">
@@ -1305,16 +1305,16 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>119148</v>
+        <v>138318</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>119148</v>
+        <v>138318</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>119148</v>
+        <v>138318</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
@@ -1326,16 +1326,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>118003</v>
+        <v>138876</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>118003</v>
+        <v>138876</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>118003</v>
+        <v>138876</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>1</v>
@@ -1347,16 +1347,16 @@
         <v>1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>335</v>
+        <v>391</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>237152</v>
+        <v>277194</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>237152</v>
+        <v>277194</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>237152</v>
+        <v>277194</v>
       </c>
       <c r="U12" s="6" t="n">
         <v>1</v>
@@ -1380,67 +1380,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>403</v>
+        <v>462</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>280916</v>
+        <v>325079</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>262228</v>
+        <v>305103</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>298309</v>
+        <v>344359</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.537543462276809</v>
+        <v>0.5199400016870342</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.5017821531525133</v>
+        <v>0.4879897249629671</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.5708256033739203</v>
+        <v>0.5507766005825726</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>322</v>
+        <v>381</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>225514</v>
+        <v>267151</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>207320</v>
+        <v>246596</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>244101</v>
+        <v>287286</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.4504246060940044</v>
+        <v>0.4480993812094337</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.4140860597102639</v>
+        <v>0.4136218620576</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.4875489171772106</v>
+        <v>0.4818713526649803</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>725</v>
+        <v>843</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>506431</v>
+        <v>592231</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>480780</v>
+        <v>562949</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>532812</v>
+        <v>620433</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.4949172686288911</v>
+        <v>0.484873638188347</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.4698499865824892</v>
+        <v>0.4608995178659543</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.5206986646598036</v>
+        <v>0.5079631143775496</v>
       </c>
     </row>
     <row r="14">
@@ -1451,67 +1451,67 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>348</v>
+        <v>433</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>241677</v>
+        <v>300146</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>224284</v>
+        <v>280866</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>260365</v>
+        <v>320122</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.4624565377231909</v>
+        <v>0.4800599983129657</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.4291743966260798</v>
+        <v>0.4492233994174273</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.4982178468474867</v>
+        <v>0.5120102750370328</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>396</v>
+        <v>473</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>275156</v>
+        <v>329037</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>256569</v>
+        <v>308902</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>293350</v>
+        <v>349592</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.5495753939059956</v>
+        <v>0.5519006187905663</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.5124510828227896</v>
+        <v>0.5181286473350197</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.5859139402897362</v>
+        <v>0.5863781379423997</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>744</v>
+        <v>906</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>516832</v>
+        <v>629182</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>490451</v>
+        <v>600980</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>542483</v>
+        <v>658464</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.5050827313711089</v>
+        <v>0.5151263618116529</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.4793013353401963</v>
+        <v>0.4920368856224505</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.5301500134175108</v>
+        <v>0.5391004821340457</v>
       </c>
     </row>
     <row r="15">
@@ -1522,16 +1522,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>751</v>
+        <v>895</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>522593</v>
+        <v>625225</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>522593</v>
+        <v>625225</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>522593</v>
+        <v>625225</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -1543,16 +1543,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>718</v>
+        <v>854</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>500670</v>
+        <v>596188</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>500670</v>
+        <v>596188</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>500670</v>
+        <v>596188</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -1564,16 +1564,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>1469</v>
+        <v>1749</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>1023263</v>
+        <v>1221413</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>1023263</v>
+        <v>1221413</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>1023263</v>
+        <v>1221413</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -1644,7 +1644,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen sobrepeso u obesidad, recogido por medición en 2016 (tasa de respuesta: 69,19%)</t>
+          <t>Menores según si tienen sobrepeso u obesidad, recogido por medición en 2016 (tasa de respuesta: 82,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1828,67 +1828,67 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>25968</v>
+        <v>31007</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>20331</v>
+        <v>24167</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>31667</v>
+        <v>37747</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.5296484093670114</v>
+        <v>0.4733691316374324</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.4146697507084505</v>
+        <v>0.3689566924164793</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.6458917090408312</v>
+        <v>0.5762673198246888</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>18887</v>
+        <v>23203</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>14113</v>
+        <v>17355</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>24231</v>
+        <v>29007</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.4905947447069675</v>
+        <v>0.4512596848107593</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.366585972655227</v>
+        <v>0.3375204866703637</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.6293835203234641</v>
+        <v>0.5641362080345921</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>44856</v>
+        <v>54210</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>36791</v>
+        <v>46171</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>51743</v>
+        <v>63279</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.5124708767998072</v>
+        <v>0.4636459037373108</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.420339162270703</v>
+        <v>0.3948897732198366</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.5911640538473062</v>
+        <v>0.5412119063833678</v>
       </c>
     </row>
     <row r="5">
@@ -1899,67 +1899,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>23061</v>
+        <v>34495</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>17362</v>
+        <v>27755</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>28698</v>
+        <v>41335</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.4703515906329886</v>
+        <v>0.5266308683625676</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.3541082909591688</v>
+        <v>0.4237326801753109</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.5853302492915494</v>
+        <v>0.6310433075835206</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>19612</v>
+        <v>28216</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>14268</v>
+        <v>22412</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>24386</v>
+        <v>34064</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.5094052552930325</v>
+        <v>0.5487403151892407</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.3706164796765361</v>
+        <v>0.4358637919654078</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.633414027344773</v>
+        <v>0.6624795133296362</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>42672</v>
+        <v>62711</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>35785</v>
+        <v>53642</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>50737</v>
+        <v>70750</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.4875291232001928</v>
+        <v>0.5363540962626893</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.4088359461526939</v>
+        <v>0.4587880936166323</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.5796608377292971</v>
+        <v>0.6051102267801636</v>
       </c>
     </row>
     <row r="6">
@@ -1970,16 +1970,16 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>49029</v>
+        <v>65502</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>49029</v>
+        <v>65502</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>49029</v>
+        <v>65502</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -1991,16 +1991,16 @@
         <v>1</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>38499</v>
+        <v>51419</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>38499</v>
+        <v>51419</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>38499</v>
+        <v>51419</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>1</v>
@@ -2012,16 +2012,16 @@
         <v>1</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>127</v>
+        <v>169</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>87528</v>
+        <v>116921</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>87528</v>
+        <v>116921</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>87528</v>
+        <v>116921</v>
       </c>
       <c r="U6" s="6" t="n">
         <v>1</v>
@@ -2045,67 +2045,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>223</v>
+        <v>264</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>157923</v>
+        <v>186908</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>142794</v>
+        <v>170828</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>173241</v>
+        <v>203540</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.4434780684965542</v>
+        <v>0.446121492495118</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.4009943101353013</v>
+        <v>0.4077392790505151</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.4864952246019911</v>
+        <v>0.4858178254580534</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>117401</v>
+        <v>129378</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>103558</v>
+        <v>114753</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>130982</v>
+        <v>144811</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.3485609237881442</v>
+        <v>0.3321748983861199</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.307463408877546</v>
+        <v>0.2946248570397408</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.3888838022173372</v>
+        <v>0.3717998226084171</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>396</v>
+        <v>457</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>275323</v>
+        <v>316286</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>256653</v>
+        <v>294424</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>296342</v>
+        <v>339329</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.3973403085441015</v>
+        <v>0.3912254068836856</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.370395872894372</v>
+        <v>0.3641833167292576</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.4276749228253662</v>
+        <v>0.419727571570486</v>
       </c>
     </row>
     <row r="8">
@@ -2116,67 +2116,67 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>280</v>
+        <v>328</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>198177</v>
+        <v>232055</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>182859</v>
+        <v>215423</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>213306</v>
+        <v>248135</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.5565219315034458</v>
+        <v>0.553878507504882</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.5135047753980088</v>
+        <v>0.5141821745419466</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.5990056898646986</v>
+        <v>0.5922607209494849</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>329</v>
+        <v>391</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>219414</v>
+        <v>260109</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>205833</v>
+        <v>244676</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>233257</v>
+        <v>274734</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.6514390762118558</v>
+        <v>0.6678251016138801</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.6111161977826627</v>
+        <v>0.6282001773915827</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.692536591122454</v>
+        <v>0.7053751429602593</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>609</v>
+        <v>719</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>417592</v>
+        <v>492164</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>396573</v>
+        <v>469121</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>436262</v>
+        <v>514026</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.6026596914558985</v>
+        <v>0.6087745931163144</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.5723250771746338</v>
+        <v>0.580272428429514</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.629604127105628</v>
+        <v>0.6358166832707424</v>
       </c>
     </row>
     <row r="9">
@@ -2187,16 +2187,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>503</v>
+        <v>592</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>356100</v>
+        <v>418963</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>356100</v>
+        <v>418963</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>356100</v>
+        <v>418963</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -2208,16 +2208,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>502</v>
+        <v>584</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>336815</v>
+        <v>389487</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>336815</v>
+        <v>389487</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>336815</v>
+        <v>389487</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -2229,16 +2229,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>1005</v>
+        <v>1176</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>692915</v>
+        <v>808450</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>692915</v>
+        <v>808450</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>692915</v>
+        <v>808450</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -2262,67 +2262,67 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>53910</v>
+        <v>66146</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>44688</v>
+        <v>56440</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>62339</v>
+        <v>75699</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.4526753684648693</v>
+        <v>0.4498624569845496</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.375239643893201</v>
+        <v>0.3838557482730113</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.5234489568835711</v>
+        <v>0.5148366581811065</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>33198</v>
+        <v>44347</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>25571</v>
+        <v>35900</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>41073</v>
+        <v>53738</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.2967169911154996</v>
+        <v>0.3246826454932012</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.2285482297549793</v>
+        <v>0.2628371095954423</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.3671028069818897</v>
+        <v>0.3934404726362971</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>130</v>
+        <v>164</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>87108</v>
+        <v>110493</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>75439</v>
+        <v>97373</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>99843</v>
+        <v>123403</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.3771292933865585</v>
+        <v>0.3895786213191445</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.3266068475178979</v>
+        <v>0.3433220820121992</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.4322635554912911</v>
+        <v>0.4350975976311745</v>
       </c>
     </row>
     <row r="11">
@@ -2333,67 +2333,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>65182</v>
+        <v>80889</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>56753</v>
+        <v>71336</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>74404</v>
+        <v>90595</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.5473246315351308</v>
+        <v>0.5501375430154504</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.476551043116429</v>
+        <v>0.4851633418188936</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.6247603561067988</v>
+        <v>0.6161442517269887</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>78687</v>
+        <v>92238</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>70812</v>
+        <v>82847</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>86314</v>
+        <v>100685</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.7032830088845005</v>
+        <v>0.6753173545067989</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.6328971930181109</v>
+        <v>0.606559527363703</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.7714517702450212</v>
+        <v>0.7371628904045577</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>209</v>
+        <v>252</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>143869</v>
+        <v>173128</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>131134</v>
+        <v>160218</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>155538</v>
+        <v>186248</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.6228707066134415</v>
+        <v>0.6104213786808556</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.567736444508709</v>
+        <v>0.5649024023688256</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.6733931524821022</v>
+        <v>0.6566779179878008</v>
       </c>
     </row>
     <row r="12">
@@ -2404,16 +2404,16 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>172</v>
+        <v>212</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>119092</v>
+        <v>147035</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>119092</v>
+        <v>147035</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>119092</v>
+        <v>147035</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
@@ -2425,16 +2425,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>167</v>
+        <v>204</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>111885</v>
+        <v>136585</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>111885</v>
+        <v>136585</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>111885</v>
+        <v>136585</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>1</v>
@@ -2446,16 +2446,16 @@
         <v>1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>339</v>
+        <v>416</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>230977</v>
+        <v>283621</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>230977</v>
+        <v>283621</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>230977</v>
+        <v>283621</v>
       </c>
       <c r="U12" s="6" t="n">
         <v>1</v>
@@ -2479,67 +2479,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>338</v>
+        <v>404</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>237801</v>
+        <v>284061</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>219700</v>
+        <v>262329</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>256707</v>
+        <v>303976</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.4536268504821084</v>
+        <v>0.4498187677890572</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.4190984251942523</v>
+        <v>0.4154058591283558</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.4896927445480223</v>
+        <v>0.4813556038517585</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>252</v>
+        <v>295</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>169486</v>
+        <v>196928</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>152738</v>
+        <v>178772</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>185334</v>
+        <v>214860</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.3478785913841982</v>
+        <v>0.3410060676206463</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.3135019948392222</v>
+        <v>0.3095667519334427</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.3804068958485285</v>
+        <v>0.3720579677346967</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>590</v>
+        <v>699</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>407287</v>
+        <v>480989</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>380987</v>
+        <v>452108</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>433598</v>
+        <v>507410</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.4026881249815326</v>
+        <v>0.3978428558400455</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.3766850554496688</v>
+        <v>0.3739540851910583</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.4287020752950155</v>
+        <v>0.4196961487405965</v>
       </c>
     </row>
     <row r="14">
@@ -2550,67 +2550,67 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>407</v>
+        <v>493</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>286420</v>
+        <v>347439</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>267514</v>
+        <v>327524</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>304521</v>
+        <v>369171</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.5463731495178916</v>
+        <v>0.5501812322109428</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.510307255451978</v>
+        <v>0.5186443961482414</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.5809015748057479</v>
+        <v>0.5845941408716442</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>474</v>
+        <v>569</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>317713</v>
+        <v>380564</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>301865</v>
+        <v>362632</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>334461</v>
+        <v>398720</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.6521214086158018</v>
+        <v>0.6589939323793537</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.6195931041514716</v>
+        <v>0.6279420322653032</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.6864980051607779</v>
+        <v>0.6904332480665573</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>881</v>
+        <v>1062</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>604134</v>
+        <v>728004</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>577823</v>
+        <v>701583</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>630434</v>
+        <v>756885</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.5973118750184674</v>
+        <v>0.6021571441599545</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.5712979247049845</v>
+        <v>0.5803038512594035</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.6233149445503311</v>
+        <v>0.626045914808942</v>
       </c>
     </row>
     <row r="15">
@@ -2621,16 +2621,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>745</v>
+        <v>897</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>524221</v>
+        <v>631500</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>524221</v>
+        <v>631500</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>524221</v>
+        <v>631500</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -2642,16 +2642,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>726</v>
+        <v>864</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>487199</v>
+        <v>577492</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>487199</v>
+        <v>577492</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>487199</v>
+        <v>577492</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -2663,16 +2663,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>1471</v>
+        <v>1761</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>1011421</v>
+        <v>1208993</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>1011421</v>
+        <v>1208993</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>1011421</v>
+        <v>1208993</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -2743,7 +2743,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen sobrepeso u obesidad, recogido por medición en 2023 (tasa de respuesta: 78,24%)</t>
+          <t>Menores según si tienen sobrepeso u obesidad, recogido por medición en 2023 (tasa de respuesta: 82,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2948,46 +2948,46 @@
         <v>0.615804472185444</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>4782</v>
+        <v>6543</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>2050</v>
+        <v>3503</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>8215</v>
+        <v>10398</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.2874581888136999</v>
+        <v>0.3394098336947229</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.1232325215070014</v>
+        <v>0.1817387800216397</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.4938848386225054</v>
+        <v>0.5394077808159854</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>15286</v>
+        <v>17047</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>10119</v>
+        <v>11410</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>20489</v>
+        <v>22563</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.3713878380120911</v>
+        <v>0.3891872659764399</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.2458659376193398</v>
+        <v>0.2604932304688486</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.497823901825025</v>
+        <v>0.5151146372893112</v>
       </c>
     </row>
     <row r="5">
@@ -3019,46 +3019,46 @@
         <v>0.7564387954354469</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>11852</v>
+        <v>12734</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>8419</v>
+        <v>8879</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>14584</v>
+        <v>15774</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.7125418111863001</v>
+        <v>0.6605901663052776</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.5061151613774948</v>
+        <v>0.4605922191840145</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.8767674784929985</v>
+        <v>0.8182612199783604</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>25872</v>
+        <v>26754</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>20669</v>
+        <v>21238</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>31039</v>
+        <v>32391</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.6286121619879089</v>
+        <v>0.61081273402356</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.5021760981749746</v>
+        <v>0.4848853627106889</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.7541340623806602</v>
+        <v>0.7395067695311516</v>
       </c>
     </row>
     <row r="6">
@@ -3090,16 +3090,16 @@
         <v>1</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>16634</v>
+        <v>19277</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>16634</v>
+        <v>19277</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>16634</v>
+        <v>19277</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>1</v>
@@ -3111,16 +3111,16 @@
         <v>1</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>41158</v>
+        <v>43801</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>41158</v>
+        <v>43801</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>41158</v>
+        <v>43801</v>
       </c>
       <c r="U6" s="6" t="n">
         <v>1</v>
@@ -3144,67 +3144,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>90308</v>
+        <v>94790</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>77992</v>
+        <v>81437</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>103921</v>
+        <v>108542</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.4508648717003198</v>
+        <v>0.4505337471229794</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.3893745757252551</v>
+        <v>0.3870645591171803</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.5188279183165703</v>
+        <v>0.5158936975028418</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>41625</v>
+        <v>44644</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>33770</v>
+        <v>36577</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>51387</v>
+        <v>55243</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.2753096060346892</v>
+        <v>0.2799202359770341</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.2233552493095119</v>
+        <v>0.2293369764653288</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.3398777164637389</v>
+        <v>0.3463762434009742</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>131933</v>
+        <v>139435</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>115930</v>
+        <v>123965</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>149213</v>
+        <v>157804</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.3753509216328321</v>
+        <v>0.3769677900730277</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.3298213534140829</v>
+        <v>0.3351453587264898</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.4245125976524962</v>
+        <v>0.4266296342804237</v>
       </c>
     </row>
     <row r="8">
@@ -3215,67 +3215,67 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>109992</v>
+        <v>115606</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>96379</v>
+        <v>101854</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>122308</v>
+        <v>128959</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.5491351282996804</v>
+        <v>0.5494662528770204</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.4811720816834298</v>
+        <v>0.4841063024971582</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.6106254242747448</v>
+        <v>0.6129354408828195</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>109567</v>
+        <v>114845</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>99805</v>
+        <v>104246</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>117422</v>
+        <v>122912</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.724690393965311</v>
+        <v>0.7200797640229657</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.6601222835362611</v>
+        <v>0.6536237565990256</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.7766447506904879</v>
+        <v>0.7706630235346709</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>219559</v>
+        <v>230450</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>202279</v>
+        <v>212081</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>235562</v>
+        <v>245920</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.6246490783671679</v>
+        <v>0.6230322099269723</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.575487402347504</v>
+        <v>0.5733703657195763</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.6701786465859173</v>
+        <v>0.6648546412735103</v>
       </c>
     </row>
     <row r="9">
@@ -3286,16 +3286,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>200300</v>
+        <v>210396</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>200300</v>
+        <v>210396</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>200300</v>
+        <v>210396</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -3307,16 +3307,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>151192</v>
+        <v>159489</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>151192</v>
+        <v>159489</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>151192</v>
+        <v>159489</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -3328,16 +3328,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>505</v>
+        <v>531</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>351492</v>
+        <v>369885</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>351492</v>
+        <v>369885</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>351492</v>
+        <v>369885</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -3361,67 +3361,67 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>21989</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>15838</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>29898</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.2931784537622616</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.2111694037037786</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.3986180673461889</v>
+      </c>
+      <c r="J10" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="D10" s="5" t="n">
-        <v>20526</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>14738</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>28201</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>0.2911882347834991</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>0.2090772560643392</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>0.4000584632053732</v>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v>29</v>
-      </c>
       <c r="K10" s="5" t="n">
-        <v>19177</v>
+        <v>19797</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>13133</v>
+        <v>14281</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>25508</v>
+        <v>26370</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.2824521057614933</v>
+        <v>0.285345629030913</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.1934223425456829</v>
+        <v>0.2058439243160959</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.3756970424642503</v>
+        <v>0.3800790150750876</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>39704</v>
+        <v>41787</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>30881</v>
+        <v>32512</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>49642</v>
+        <v>52270</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.2869020507514308</v>
+        <v>0.2894145600858432</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.2231466658670435</v>
+        <v>0.2251823057845045</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.3587204073974344</v>
+        <v>0.3620247346169958</v>
       </c>
     </row>
     <row r="11">
@@ -3432,67 +3432,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>49965</v>
+        <v>53014</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>42290</v>
+        <v>45105</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>55753</v>
+        <v>59165</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.7088117652165009</v>
+        <v>0.7068215462377385</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.5999415367946266</v>
+        <v>0.6013819326538112</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.7909227439356611</v>
+        <v>0.7888305962962212</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>48719</v>
+        <v>49583</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>42388</v>
+        <v>43010</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>54763</v>
+        <v>55099</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.7175478942385064</v>
+        <v>0.7146543709690868</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.6243029575357499</v>
+        <v>0.6199209849249123</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.8065776574543171</v>
+        <v>0.7941560756839036</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>98683</v>
+        <v>102596</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>88745</v>
+        <v>92113</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>107506</v>
+        <v>111871</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.7130979492485693</v>
+        <v>0.7105854399141567</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.6412795926025657</v>
+        <v>0.6379752653830045</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.7768533341329565</v>
+        <v>0.7748176942154954</v>
       </c>
     </row>
     <row r="12">
@@ -3503,16 +3503,16 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>70491</v>
+        <v>75003</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>70491</v>
+        <v>75003</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>70491</v>
+        <v>75003</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
@@ -3524,16 +3524,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>67896</v>
+        <v>69380</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>67896</v>
+        <v>69380</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>67896</v>
+        <v>69380</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>1</v>
@@ -3545,16 +3545,16 @@
         <v>1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>138387</v>
+        <v>144383</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>138387</v>
+        <v>144383</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>138387</v>
+        <v>144383</v>
       </c>
       <c r="U12" s="6" t="n">
         <v>1</v>
@@ -3578,67 +3578,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>121338</v>
+        <v>127284</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>106201</v>
+        <v>111836</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>137074</v>
+        <v>145071</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.410877839109871</v>
+        <v>0.4106948042901157</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.3596202801771443</v>
+        <v>0.360849822429133</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.4641609216140092</v>
+        <v>0.4680858711282094</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>65584</v>
+        <v>70984</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>55698</v>
+        <v>59504</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>77825</v>
+        <v>82803</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.2782241723445429</v>
+        <v>0.2860584886184616</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.2362883060635219</v>
+        <v>0.2397956487304755</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.3301576549105049</v>
+        <v>0.3336870490922481</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>186922</v>
+        <v>198268</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>168051</v>
+        <v>178897</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>207975</v>
+        <v>219468</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.3519941824153193</v>
+        <v>0.3552752365535039</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.3164587096881991</v>
+        <v>0.3205643724097117</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.3916401595218164</v>
+        <v>0.3932631680112414</v>
       </c>
     </row>
     <row r="14">
@@ -3649,67 +3649,67 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>173977</v>
+        <v>182639</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>158241</v>
+        <v>164852</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>189114</v>
+        <v>198087</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.589122160890129</v>
+        <v>0.5893051957098844</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.5358390783859908</v>
+        <v>0.53191412887179</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.6403797198228557</v>
+        <v>0.6391501775708668</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>170138</v>
+        <v>177161</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>157897</v>
+        <v>165342</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>180024</v>
+        <v>188641</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.721775827655457</v>
+        <v>0.7139415113815384</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.669842345089495</v>
+        <v>0.6663129509077519</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.7637116939364781</v>
+        <v>0.7602043512695245</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>494</v>
+        <v>516</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>344115</v>
+        <v>359800</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>323062</v>
+        <v>338600</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>362986</v>
+        <v>379171</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.6480058175846806</v>
+        <v>0.6447247634464961</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.6083598404781836</v>
+        <v>0.6067368319887586</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.683541290311801</v>
+        <v>0.6794356275902882</v>
       </c>
     </row>
     <row r="15">
@@ -3720,16 +3720,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>295315</v>
+        <v>309923</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>295315</v>
+        <v>309923</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>295315</v>
+        <v>309923</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -3741,16 +3741,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>356</v>
+        <v>375</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>235722</v>
+        <v>248145</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>235722</v>
+        <v>248145</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>235722</v>
+        <v>248145</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -3762,16 +3762,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>765</v>
+        <v>804</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>531037</v>
+        <v>558068</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>531037</v>
+        <v>558068</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>531037</v>
+        <v>558068</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
